--- a/sample_data/confirmation_of_faculty_loading_sample.xlsx
+++ b/sample_data/confirmation_of_faculty_loading_sample.xlsx
@@ -32,7 +32,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Faculty Member</t>
+          <t>Ramon Villanueva</t>
         </is>
       </c>
     </row>
